--- a/experiment/HAT+CNN_2CH_bestx4/Test/results-Set5/Set5.xlsx
+++ b/experiment/HAT+CNN_2CH_bestx4/Test/results-Set5/Set5.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33.74</v>
+        <v>33.75</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8942</v>
+        <v>0.8944</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.92</v>
+        <v>34.95</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9422</v>
+        <v>0.9424</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.79</v>
+        <v>28.82</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9206</v>
+        <v>0.9212</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.99</v>
+        <v>33</v>
       </c>
       <c r="C5" t="n">
         <v>0.7985</v>
@@ -507,7 +507,7 @@
         <v>30.87</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9151</v>
+        <v>0.9152</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.26</v>
+        <v>32.28</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8942</v>
+        <v>0.8943</v>
       </c>
     </row>
   </sheetData>
